--- a/AAII_Financials/Yearly/QNC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/QNC_YR_FIN.xlsx
@@ -2444,7 +2444,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-19200</v>
+        <v>-19500</v>
       </c>
       <c r="E72" s="3">
         <v>-11200</v>
